--- a/Rental Calc Template.xlsx
+++ b/Rental Calc Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janus\Documents\Chat GPT Upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11F7087-718C-4185-8EF5-9344E7DE2F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF2CAF8-E84D-4C7D-9A1F-C3F8719472AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="951" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -889,7 +889,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1147,13 +1147,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1213,6 +1214,9 @@
     <xf numFmtId="44" fontId="10" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1234,12 +1238,6 @@
     <xf numFmtId="44" fontId="10" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1686,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="15"/>
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="117" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="76"/>
@@ -1706,7 +1704,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="88" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="76"/>
@@ -1743,7 +1741,7 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="62"/>
-      <c r="D12" s="90">
+      <c r="D12" s="89">
         <v>10000</v>
       </c>
       <c r="E12" s="73"/>
@@ -1905,10 +1903,10 @@
         <v>11300</v>
       </c>
       <c r="E23" s="43"/>
-      <c r="F23" s="124" t="s">
+      <c r="F23" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="125">
+      <c r="G23" s="126">
         <f>$G$16*10</f>
         <v>4603.4500000000007</v>
       </c>
@@ -2015,10 +2013,10 @@
         <f>G15</f>
         <v>1299.5</v>
       </c>
-      <c r="F31" s="117" t="s">
+      <c r="F31" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="G31" s="119">
+      <c r="G31" s="120">
         <f>IF(B16&gt;0,($D$12*50%),0)</f>
         <v>5000</v>
       </c>
@@ -2034,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="47"/>
-      <c r="F32" s="118"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="103"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
@@ -2047,7 +2045,7 @@
         <f>IF(D21=1,G14-D26,IF(D21=2,G14/2,IF(D21=3,G14/3)))</f>
         <v>1071.239999999998</v>
       </c>
-      <c r="F33" s="118"/>
+      <c r="F33" s="119"/>
       <c r="G33" s="103"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
@@ -2061,7 +2059,7 @@
         <v>8929.260000000002</v>
       </c>
       <c r="E34" s="43"/>
-      <c r="F34" s="118"/>
+      <c r="F34" s="119"/>
       <c r="G34" s="103"/>
     </row>
     <row r="35" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.35">
@@ -2070,10 +2068,10 @@
       <c r="C35" s="55"/>
       <c r="D35" s="56"/>
       <c r="E35" s="56"/>
-      <c r="F35" s="120" t="s">
+      <c r="F35" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="G35" s="122">
+      <c r="G35" s="123">
         <f>IF(B16&gt;0,($D$12*5),0)</f>
         <v>50000</v>
       </c>
@@ -2086,7 +2084,7 @@
       <c r="C36" s="54"/>
       <c r="D36" s="54"/>
       <c r="E36" s="38"/>
-      <c r="F36" s="118"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="103"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
@@ -2100,7 +2098,7 @@
         <v>11300</v>
       </c>
       <c r="E37" s="43"/>
-      <c r="F37" s="118"/>
+      <c r="F37" s="119"/>
       <c r="G37" s="103"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2113,8 +2111,8 @@
         <f>G15</f>
         <v>1299.5</v>
       </c>
-      <c r="F38" s="121"/>
-      <c r="G38" s="123"/>
+      <c r="F38" s="122"/>
+      <c r="G38" s="124"/>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A39" s="48" t="s">
@@ -2359,14 +2357,14 @@
       <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="126">
+      <c r="B8" s="90">
         <v>1</v>
       </c>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="128"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="76"/>
       <c r="J8" s="17"/>
     </row>
     <row r="10" spans="1:12" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -2377,7 +2375,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="88" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="76"/>
@@ -2412,7 +2410,7 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="62"/>
-      <c r="D12" s="90"/>
+      <c r="D12" s="89"/>
       <c r="E12" s="73"/>
       <c r="F12" s="9"/>
       <c r="G12" s="24"/>
@@ -2484,10 +2482,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B16" s="11">
-        <v>3.1E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="80">
